--- a/Trip_Data_Store/NJ_Veterans_Sample.xlsx
+++ b/Trip_Data_Store/NJ_Veterans_Sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kshema/python/Four-Line-Travels/Trip_Data_Store/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78DC976-8533-1E4E-AD2E-2162DF75C002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC03665D-BDAB-AF44-ADA5-12A4B12C4F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6160" yWindow="2520" windowWidth="28040" windowHeight="17440" xr2:uid="{18F0F317-B38D-9C4A-97FC-C56FD74F98AA}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Destination Address</t>
   </si>
   <si>
-    <t>Roundtrip or One-Way</t>
-  </si>
-  <si>
     <t>Number of Hours</t>
   </si>
   <si>
@@ -81,6 +78,9 @@
   </si>
   <si>
     <t>Komalan</t>
+  </si>
+  <si>
+    <t>Type of service</t>
   </si>
 </sst>
 </file>
@@ -472,6 +472,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
+    <col min="5" max="5" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -488,27 +489,27 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3">
         <v>46084</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="F2" s="2">
         <v>2.5</v>
@@ -516,19 +517,19 @@
     </row>
     <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3">
         <v>46085</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
         <v>1.5</v>
@@ -536,19 +537,19 @@
     </row>
     <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3">
         <v>46086</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
@@ -556,19 +557,19 @@
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3">
         <v>46087</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
         <v>2</v>
@@ -576,19 +577,19 @@
     </row>
     <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="3">
         <v>46088</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
